--- a/Comparables MSCI - Huella.xlsx
+++ b/Comparables MSCI - Huella.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Mesa de Inversiones\Bottom-Up\2 Proceso de Inversión Renta Fija\Corporates - Emisiones\Crédito - BU\3. ESG\9. ESG Manager - MSCI\2. Reportes\Medición Huella de Carbono\Huella Total  (SURA e Integra)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Mesa de Inversiones\Bottom-Up\2 Proceso de Inversión Renta Fija\Corporates - Emisiones\Crédito - BU\3. ESG\9. ESG Manager - MSCI\2. Reportes\Medición Huella de Carbono\Python\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FC67D2F-7B8B-41E4-BA2E-43B1C8D7C6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F8ADAB9-453D-4FC4-BA10-1B32F1CED96B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="202606" sheetId="1" r:id="rId1"/>
-    <sheet name="202512" sheetId="2" r:id="rId2"/>
+    <sheet name="202512" sheetId="2" r:id="rId1"/>
+    <sheet name="202605" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="IQ_CH">110000</definedName>
@@ -500,7 +500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC13AC14-A98D-4C93-9EFA-17279F63769D}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -536,7 +536,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="2">
-        <v>109.30923404000001</v>
+        <v>145.75331588</v>
       </c>
       <c r="D2" s="2">
         <v>202.59174264999999</v>
@@ -553,7 +553,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="2">
-        <v>387.76501610999998</v>
+        <v>388.10195901999998</v>
       </c>
       <c r="D3" s="2">
         <v>682.78964388999998</v>
@@ -570,7 +570,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="2">
-        <v>33.89263287</v>
+        <v>39.567476790000001</v>
       </c>
       <c r="D4" s="2">
         <v>202.59174264999999</v>
@@ -587,7 +587,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="2">
-        <v>186.51269511000001</v>
+        <v>202.57506538000001</v>
       </c>
       <c r="D5" s="2">
         <v>221.46725343</v>
@@ -602,15 +602,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACA1B2CA-5A6A-4EEC-BC15-43172DA05197}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="2" max="2" width="43.453125" customWidth="1"/>
     <col min="3" max="3" width="38.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="44.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -641,7 +641,7 @@
         <v>109.30923404000001</v>
       </c>
       <c r="D2" s="2">
-        <v>212.76086000000001</v>
+        <v>202.59174264999999</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -655,10 +655,10 @@
         <v>9</v>
       </c>
       <c r="C3" s="2">
-        <v>398.4579</v>
+        <v>388.10195901999998</v>
       </c>
       <c r="D3" s="2">
-        <v>689.74564899999996</v>
+        <v>682.78964388999998</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>10</v>
@@ -672,10 +672,10 @@
         <v>12</v>
       </c>
       <c r="C4" s="2">
-        <v>33.89263287</v>
+        <v>33.985581330000002</v>
       </c>
       <c r="D4" s="2">
-        <v>212.76086000000001</v>
+        <v>202.59174264999999</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>13</v>
@@ -689,10 +689,10 @@
         <v>15</v>
       </c>
       <c r="C5" s="2">
-        <v>186.51269511000001</v>
+        <v>186.25221411000001</v>
       </c>
       <c r="D5" s="2">
-        <v>227.34513200000001</v>
+        <v>221.46725343</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>16</v>
